--- a/seed-data/demo/Dodge_Weekly_Export_2026-09-29.xlsx
+++ b/seed-data/demo/Dodge_Weekly_Export_2026-09-29.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DG-26-114872</t>
+          <t>DG-PT4872</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DG-26-115390</t>
+          <t>DG-BH5390</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DG-26-116004</t>
+          <t>DG-BC6004</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
